--- a/23-06-26/Umair.xlsx
+++ b/23-06-26/Umair.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19727018-5DB9-41BD-A51F-167868C1EA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ACB8B3-3CD6-4DE4-81E4-9A6302CDB050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="122">
   <si>
     <t>Gm</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>Shop Bill Summary (Umair)</t>
+  </si>
+  <si>
+    <t>B912371</t>
   </si>
 </sst>
 </file>
@@ -23431,7 +23434,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>6583.1257695000004</v>
+        <v>6359.0411205</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23541,15 +23544,15 @@
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>1322.22288</v>
+        <v>1296.95694</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>42.153828599999997</v>
+        <v>42.027498899999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>7059.7057086000004</v>
+        <v>7034.3134388999997</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23615,15 +23618,15 @@
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>1397.4750899999999</v>
+        <v>1360.6254300000001</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>44.208889650000003</v>
+        <v>44.024641349999996</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>7426.6059796499994</v>
+        <v>7389.5720713499995</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23689,15 +23692,15 @@
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>1150.48164</v>
+        <v>1115.7304799999999</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>37.916537399999996</v>
+        <v>37.742781600000001</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>6208.0101773999995</v>
+        <v>6173.0852615999993</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23759,15 +23762,15 @@
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1818.6150399999999</v>
+        <v>1743.06944</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>64.145478400000002</v>
+        <v>47.141907199999999</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>9568.0725184000003</v>
+        <v>9475.5233472</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23775,7 +23778,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>1687.7686080000001</v>
+        <v>1598.1860543999999</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23829,15 +23832,15 @@
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1844.1843199999998</v>
+        <v>1777.3555199999998</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>65.624428800000004</v>
+        <v>48.9840576</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>9929.2647487999984</v>
+        <v>9845.7955775999999</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23899,15 +23902,15 @@
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1617.2569599999999</v>
+        <v>1577.15968</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>44.842124800000008</v>
+        <v>44.641638400000005</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>9013.2670847999998</v>
+        <v>8972.9693184000007</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -24170,15 +24173,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>9150.2359300000007</v>
+        <v>8870.8974900000012</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>298.89128764999998</v>
+        <v>264.56252504999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>49204.926217649998</v>
+        <v>48891.259015049996</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24308,7 +24311,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>49204.926217649998</v>
+        <v>48891.259015050004</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24430,7 +24433,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>9150.2359300000007</v>
+        <v>8870.8974900000012</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24452,7 +24455,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>48906.034930000009</v>
+        <v>48626.696490000009</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24477,7 +24480,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>1222.6508732500004</v>
+        <v>1215.6674122500003</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24487,7 +24490,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>50128.685803250009</v>
+        <v>49842.363902250007</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24830,11 +24833,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -24855,7 +24858,7 @@
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="228"/>
       <c r="B13" s="168">
-        <v>0</v>
+        <v>3277876165058</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -24943,7 +24946,7 @@
       <c r="M15" s="250"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
@@ -25005,15 +25008,15 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>138.96266999999997</v>
+        <v>113.69672999999997</v>
       </c>
       <c r="O16" s="107">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>3.5907433499999999</v>
+        <v>3.4644136499999996</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>721.73941334999995</v>
+        <v>696.34714364999991</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -25069,15 +25072,15 @@
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>202.67313000000001</v>
+        <v>165.82346999999999</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" si="1"/>
-        <v>5.3572606500000006</v>
+        <v>5.1730123500000005</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="2"/>
-        <v>1076.8093906500001</v>
+        <v>1039.7754823499999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25131,15 +25134,15 @@
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>191.13138000000001</v>
+        <v>156.38021999999998</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="1"/>
-        <v>5.2995519</v>
+        <v>5.1257961000000005</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="2"/>
-        <v>1065.2099319000001</v>
+        <v>1030.2850160999999</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25191,15 +25194,15 @@
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>252.49663999999999</v>
+        <v>206.58815999999996</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="1"/>
-        <v>6.2746431999999999</v>
+        <v>6.0451007999999993</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="2"/>
-        <v>1261.2032831999998</v>
+        <v>1215.0652607999998</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25249,15 +25252,15 @@
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>180.43775999999997</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="1"/>
-        <v>6.1148351999999999</v>
+        <v>5.9143487999999991</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="2"/>
-        <v>1229.0818752</v>
+        <v>1188.7841087999998</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25307,15 +25310,15 @@
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>180.43775999999997</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="1"/>
-        <v>6.1148351999999999</v>
+        <v>5.9143487999999991</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="2"/>
-        <v>1229.0818752</v>
+        <v>1188.7841087999998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25522,15 +25525,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1226.3339000000001</v>
+        <v>1003.3641</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>32.751869500000005</v>
+        <v>31.637020499999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>6583.1257694999986</v>
+        <v>6359.0411204999991</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25665,11 +25668,11 @@
       </c>
       <c r="O32" s="156">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1226.3339000000001</v>
+        <v>1003.3641</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25691,7 +25694,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>6550.3739000000005</v>
+        <v>6327.4040999999997</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25716,7 +25719,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>32.751869500000005</v>
+        <v>31.637020499999998</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25726,7 +25729,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>6583.1257695000004</v>
+        <v>6359.0411205</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30949,8 +30952,8 @@
       <c r="A10" s="227" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="75">
-        <v>0</v>
+      <c r="B10" s="75" t="s">
+        <v>121</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -30974,11 +30977,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="227"/>
       <c r="B11" s="76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -31000,11 +31003,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -31024,8 +31027,8 @@
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="228"/>
-      <c r="B13" s="64">
-        <v>0</v>
+      <c r="B13" s="75" t="s">
+        <v>121</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -31113,11 +31116,11 @@
       <c r="M15" s="250"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" s="94" t="s">
         <v>1</v>
@@ -31351,15 +31354,15 @@
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>163.00415999999998</v>
+        <v>133.36704</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>20.782304</v>
+        <v>4.0082751999999999</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>852.07446399999992</v>
+        <v>805.66331519999994</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31409,15 +31412,15 @@
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>147.02336</v>
+        <v>120.29183999999999</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>20.382784000000001</v>
+        <v>3.9428991999999998</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>835.69414400000005</v>
+        <v>792.52273920000005</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31680,15 +31683,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>310.02751999999998</v>
+        <v>253.65888000000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>41.165087999999997</v>
+        <v>7.9511743999999993</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1687.7686079999999</v>
+        <v>1598.1860544000001</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31823,11 +31826,11 @@
       </c>
       <c r="O32" s="156">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>310.02751999999998</v>
+        <v>253.65888000000001</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31849,7 +31852,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1646.6035200000001</v>
+        <v>1590.23488</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31870,11 +31873,11 @@
       </c>
       <c r="O34" s="159">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>41.165088000000004</v>
+        <v>7.9511744000000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31884,7 +31887,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1687.7686080000001</v>
+        <v>1598.1860543999999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
